--- a/only_night_off_emp_df_class.xlsx
+++ b/only_night_off_emp_df_class.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -58,12 +55,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,118 +481,42 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>LineID</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>MonthOTNew</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTDOTAvgNew</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>OJTCode</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>SkillName</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Shift_Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>88748137</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ME/MOE6-CN</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>ME/MFO6.5-CN</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>女</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>BSFA12</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="M2" t="n">
-        <v>36</v>
-      </c>
-      <c r="N2" t="n">
-        <v>34.67</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>OJT3116</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>ECU VI</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>N</t>
         </is>
       </c>
     </row>
